--- a/aggregates/input/Aggregates Price List.xlsx
+++ b/aggregates/input/Aggregates Price List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moosemarketer/Code/garoppos/collectors/aggregates/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4708EBC3-229C-B84F-AC9E-E2AA75D582D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C537C6F5-A07D-DE42-BB9C-435D997D01FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="35440" windowHeight="19800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="123">
   <si>
     <t>Yard</t>
   </si>
@@ -148,9 +148,6 @@
     <t>3/4" Jersey Yellow Stone</t>
   </si>
   <si>
-    <t>3/4" Pink Carnation Stone</t>
-  </si>
-  <si>
     <t>3/4" Light Grey Quarry Blend Stone</t>
   </si>
   <si>
@@ -367,9 +364,6 @@
     <t>Blue</t>
   </si>
   <si>
-    <t>Pink Carnation</t>
-  </si>
-  <si>
     <t>Dark Grey Quarry Blend</t>
   </si>
   <si>
@@ -392,9 +386,6 @@
   </si>
   <si>
     <t>24615_three_quarter_inch_blue_stone.jpeg</t>
-  </si>
-  <si>
-    <t>38971_three_quarter_inch_pink_carnation_stone.jpeg</t>
   </si>
   <si>
     <t>24612_three_eigth_inch_jersey_yellow_stone.jpeg</t>
@@ -1023,7 +1014,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{890BC82B-2B5C-D149-BACA-91D13960B509}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="42.5" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="4" customWidth="1"/>
@@ -1045,10 +1036,10 @@
         <v>29</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>28</v>
@@ -1060,19 +1051,19 @@
         <v>32</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="19">
@@ -1083,10 +1074,10 @@
         <v>5071</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" s="8">
         <v>33</v>
@@ -1095,7 +1086,7 @@
         <v>19</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>0</v>
@@ -1104,7 +1095,7 @@
         <v>1</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="19">
@@ -1115,10 +1106,10 @@
         <v>5071</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E3" s="8">
         <v>33</v>
@@ -1127,7 +1118,7 @@
         <v>19</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>0</v>
@@ -1136,7 +1127,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="19">
@@ -1147,10 +1138,10 @@
         <v>5071</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" s="8">
         <v>33</v>
@@ -1159,7 +1150,7 @@
         <v>19</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>0</v>
@@ -1168,7 +1159,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="19">
@@ -1179,7 +1170,7 @@
         <v>5071</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>2</v>
@@ -1191,7 +1182,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>0</v>
@@ -1200,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="19">
@@ -1211,7 +1202,7 @@
         <v>5071</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>3</v>
@@ -1223,7 +1214,7 @@
         <v>28</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>0</v>
@@ -1232,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="19">
@@ -1243,7 +1234,7 @@
         <v>5071</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>4</v>
@@ -1255,7 +1246,7 @@
         <v>4</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>0</v>
@@ -1264,7 +1255,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="19">
@@ -1275,7 +1266,7 @@
         <v>5071</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>5</v>
@@ -1287,7 +1278,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>0</v>
@@ -1296,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="19">
@@ -1307,7 +1298,7 @@
         <v>18163</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>6</v>
@@ -1325,7 +1316,7 @@
         <v>7</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="19">
@@ -1336,7 +1327,7 @@
         <v>24605</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>8</v>
@@ -1354,7 +1345,7 @@
         <v>7</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="19">
@@ -1365,7 +1356,7 @@
         <v>13878</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>10</v>
@@ -1383,7 +1374,7 @@
         <v>7</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="19">
@@ -1394,7 +1385,7 @@
         <v>24603</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>11</v>
@@ -1412,7 +1403,7 @@
         <v>7</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="19">
@@ -1423,7 +1414,7 @@
         <v>24604</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>12</v>
@@ -1441,7 +1432,7 @@
         <v>7</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="19">
@@ -1452,7 +1443,7 @@
         <v>24601</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>13</v>
@@ -1464,7 +1455,7 @@
         <v>12.5</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>9</v>
@@ -1473,7 +1464,7 @@
         <v>7</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="19">
@@ -1484,7 +1475,7 @@
         <v>24601</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>14</v>
@@ -1496,7 +1487,7 @@
         <v>10.5</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>9</v>
@@ -1505,7 +1496,7 @@
         <v>7</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19">
@@ -1516,7 +1507,7 @@
         <v>24601</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>15</v>
@@ -1528,7 +1519,7 @@
         <v>21</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>9</v>
@@ -1537,7 +1528,7 @@
         <v>7</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="19">
@@ -1548,10 +1539,10 @@
         <v>24608</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" s="8">
         <v>40</v>
@@ -1560,7 +1551,7 @@
         <v>28</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>9</v>
@@ -1569,7 +1560,7 @@
         <v>7</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="19">
@@ -1580,7 +1571,7 @@
         <v>24612</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>33</v>
@@ -1592,10 +1583,10 @@
         <v>18.87</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>9</v>
@@ -1604,7 +1595,7 @@
         <v>7</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="19">
@@ -1615,7 +1606,7 @@
         <v>24612</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>35</v>
@@ -1627,10 +1618,10 @@
         <v>39.619999999999997</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>9</v>
@@ -1639,7 +1630,7 @@
         <v>7</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="19">
@@ -1650,7 +1641,7 @@
         <v>24613</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>16</v>
@@ -1662,10 +1653,10 @@
         <v>40.9</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>9</v>
@@ -1674,7 +1665,7 @@
         <v>7</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="19">
@@ -1685,7 +1676,7 @@
         <v>24613</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>18</v>
@@ -1697,10 +1688,10 @@
         <v>37.25</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>9</v>
@@ -1709,7 +1700,7 @@
         <v>7</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="19">
@@ -1720,7 +1711,7 @@
         <v>24614</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>34</v>
@@ -1732,10 +1723,10 @@
         <v>70</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>9</v>
@@ -1744,7 +1735,7 @@
         <v>7</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="19">
@@ -1755,10 +1746,10 @@
         <v>24614</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E23" s="8">
         <v>93</v>
@@ -1767,10 +1758,10 @@
         <v>70</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>9</v>
@@ -1779,7 +1770,7 @@
         <v>7</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="19">
@@ -1790,10 +1781,10 @@
         <v>24614</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E24" s="8">
         <v>95</v>
@@ -1802,10 +1793,10 @@
         <v>76</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>9</v>
@@ -1814,7 +1805,7 @@
         <v>22</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="19">
@@ -1825,10 +1816,10 @@
         <v>24629</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E25" s="8">
         <v>95</v>
@@ -1837,10 +1828,10 @@
         <v>76</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>9</v>
@@ -1849,7 +1840,7 @@
         <v>21</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="19">
@@ -1860,10 +1851,10 @@
         <v>24629</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E26" s="8">
         <v>95</v>
@@ -1872,10 +1863,10 @@
         <v>76</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>9</v>
@@ -1884,7 +1875,7 @@
         <v>26</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="19">
@@ -1895,10 +1886,10 @@
         <v>24616</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27" s="8">
         <v>46</v>
@@ -1907,10 +1898,10 @@
         <v>31.5</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>9</v>
@@ -1919,7 +1910,7 @@
         <v>7</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="19">
@@ -1930,7 +1921,7 @@
         <v>24616</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>19</v>
@@ -1942,10 +1933,10 @@
         <v>31.5</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>9</v>
@@ -1954,7 +1945,7 @@
         <v>22</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="19">
@@ -1965,10 +1956,10 @@
         <v>24617</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E29" s="8">
         <v>46</v>
@@ -1977,16 +1968,16 @@
         <v>31.5</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="19">
@@ -1997,7 +1988,7 @@
         <v>24615</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>17</v>
@@ -2009,10 +2000,10 @@
         <v>35</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>9</v>
@@ -2021,7 +2012,7 @@
         <v>7</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="19">
@@ -2032,7 +2023,7 @@
         <v>24615</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>27</v>
@@ -2044,10 +2035,10 @@
         <v>35.5</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>9</v>
@@ -2056,33 +2047,33 @@
         <v>23</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="19">
       <c r="A32" s="4">
-        <v>38971</v>
+        <v>24622</v>
       </c>
       <c r="B32" s="4">
-        <v>38971</v>
+        <v>24622</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E32" s="8">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="F32" s="8">
-        <v>100</v>
+        <v>28.25</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>9</v>
@@ -2091,18 +2082,18 @@
         <v>7</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="19">
       <c r="A33" s="4">
-        <v>24622</v>
+        <v>24623</v>
       </c>
       <c r="B33" s="4">
-        <v>24622</v>
+        <v>24623</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>37</v>
@@ -2114,65 +2105,65 @@
         <v>28.25</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="K33" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="19">
       <c r="A34" s="4">
-        <v>24623</v>
+        <v>24611</v>
       </c>
       <c r="B34" s="4">
-        <v>24623</v>
+        <v>24611</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E34" s="8">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="F34" s="8">
-        <v>28.25</v>
+        <v>78</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="J34" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="K34" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="19">
       <c r="A35" s="4">
-        <v>24611</v>
+        <v>24620</v>
       </c>
       <c r="B35" s="4">
         <v>24611</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E35" s="8">
         <v>98</v>
@@ -2181,7 +2172,7 @@
         <v>78</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H35" s="8" t="s">
         <v>87</v>
@@ -2193,18 +2184,18 @@
         <v>23</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="19">
       <c r="A36" s="4">
-        <v>24620</v>
+        <v>24621</v>
       </c>
       <c r="B36" s="4">
         <v>24611</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>40</v>
@@ -2216,7 +2207,7 @@
         <v>78</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H36" s="8" t="s">
         <v>88</v>
@@ -2228,65 +2219,65 @@
         <v>23</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="19">
       <c r="A37" s="4">
-        <v>24621</v>
+        <v>29273</v>
       </c>
       <c r="B37" s="4">
-        <v>24611</v>
+        <v>29273</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="E37" s="8">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F37" s="8">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>9</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="19">
       <c r="A38" s="4">
-        <v>29273</v>
+        <v>24705</v>
       </c>
       <c r="B38" s="4">
-        <v>29273</v>
+        <v>24705</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="E38" s="8">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="F38" s="8">
-        <v>68</v>
+        <v>31.5</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>92</v>
@@ -2295,71 +2286,36 @@
         <v>9</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="19">
       <c r="A39" s="4">
-        <v>24705</v>
+        <v>30120</v>
       </c>
       <c r="B39" s="4">
-        <v>24705</v>
+        <v>30120</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E39" s="8">
-        <v>51</v>
+        <v>205</v>
       </c>
       <c r="F39" s="8">
-        <v>31.5</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="19">
-      <c r="A40" s="4">
-        <v>30120</v>
-      </c>
-      <c r="B40" s="4">
-        <v>30120</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="8">
-        <v>205</v>
-      </c>
-      <c r="F40" s="8">
-        <v>115</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
